--- a/results/diagnostics/20_FINAL_DIAGNOSTICS.xlsx
+++ b/results/diagnostics/20_FINAL_DIAGNOSTICS.xlsx
@@ -535,16 +535,16 @@
         <v>65</v>
       </c>
       <c r="C6" t="n">
-        <v>119.072624615385</v>
+        <v>104.149458461538</v>
       </c>
       <c r="D6" t="n">
-        <v>45.1934591309062</v>
+        <v>40.0548247323976</v>
       </c>
       <c r="E6" t="n">
-        <v>37.144</v>
+        <v>32.5535</v>
       </c>
       <c r="F6" t="n">
-        <v>236.3</v>
+        <v>214.38</v>
       </c>
     </row>
   </sheetData>
@@ -589,7 +589,7 @@
         <v>-0.140542314573349</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.243912696359426</v>
+        <v>-0.224133224981777</v>
       </c>
     </row>
     <row r="3">
@@ -606,7 +606,7 @@
         <v>-0.284463902291939</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1925789708053</v>
+        <v>-0.157154889642264</v>
       </c>
     </row>
     <row r="4">
@@ -623,7 +623,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0201407131616609</v>
+        <v>0.00277627344317959</v>
       </c>
     </row>
     <row r="5">
@@ -631,13 +631,13 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.243912696359426</v>
+        <v>-0.224133224981777</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1925789708053</v>
+        <v>-0.157154889642264</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0201407131616609</v>
+        <v>0.00277627344317959</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -685,7 +685,7 @@
         <v>0.0292106195330673</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.257116502896031</v>
+        <v>-0.239818049655522</v>
       </c>
     </row>
     <row r="3">
@@ -702,7 +702,7 @@
         <v>-0.435528024934217</v>
       </c>
       <c r="E3" t="n">
-        <v>0.133118667771508</v>
+        <v>0.157116459437503</v>
       </c>
     </row>
     <row r="4">
@@ -719,7 +719,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0796730701805873</v>
+        <v>-0.0797494676159823</v>
       </c>
     </row>
     <row r="5">
@@ -727,13 +727,13 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.257116502896031</v>
+        <v>-0.239818049655522</v>
       </c>
       <c r="C5" t="n">
-        <v>0.133118667771508</v>
+        <v>0.157116459437503</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0796730701805873</v>
+        <v>-0.0797494676159823</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -793,7 +793,7 @@
         <v>0.725008373099377</v>
       </c>
       <c r="G2" t="n">
-        <v>38.7507588060031</v>
+        <v>37.5384509744222</v>
       </c>
     </row>
     <row r="3">
@@ -816,7 +816,7 @@
         <v>0.530691286782258</v>
       </c>
       <c r="G3" t="n">
-        <v>24.4617277512423</v>
+        <v>24.5716821749299</v>
       </c>
     </row>
     <row r="4">
@@ -839,7 +839,7 @@
         <v>0.583417245394264</v>
       </c>
       <c r="G4" t="n">
-        <v>43.5849523450115</v>
+        <v>39.418694759543</v>
       </c>
     </row>
     <row r="5">
@@ -862,7 +862,7 @@
         <v>0.593716553096843</v>
       </c>
       <c r="G5" t="n">
-        <v>25.3811219982036</v>
+        <v>25.6304878708656</v>
       </c>
     </row>
     <row r="6">
@@ -885,7 +885,7 @@
         <v>0.612586091968236</v>
       </c>
       <c r="G6" t="n">
-        <v>22.2229348319046</v>
+        <v>21.4798924960275</v>
       </c>
     </row>
   </sheetData>
